--- a/forms/trg/Formulir_TRG_geosus.xlsx
+++ b/forms/trg/Formulir_TRG_geosus.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B30)</f>
+        <f>COUNTA(Anggota!B5:B31)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F30)</f>
+        <f>COUNTA(Anggota!F5:F31)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,20 +913,16 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Muh. Jayadi,MP</t>
+          <t>Prof. Dr. Ir. Rismaneswati, MP</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Soil fertility jayaditanahunhas@gmail.com</t>
-        </is>
-      </c>
+      <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
@@ -946,18 +942,18 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Asmita Ahmad, ST, M.Si​</t>
+          <t>Prof. Dr. Ir. Muh. Jayadi,MP</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Soil Mineralogy for Genesis and Landslide asmita.ahmad@agri.unhas.ac.id</t>
+          <t>Soil fertility jayaditanahunhas@gmail.com</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -979,18 +975,18 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Ir. Syamsul Arifin Lias, M.Si​</t>
+          <t>Dr. Asmita Ahmad, ST, M.Si​</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Soil Mineralogy for Genesis and Landslide syam_lias@yahoo.com</t>
+          <t>Soil Mineralogy for Genesis and Landslide asmita.ahmad@agri.unhas.ac.id</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1012,18 +1008,18 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Zulkarnain, Chairuddin, MP​</t>
+          <t>Ir. Syamsul Arifin Lias, M.Si​</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Landuse Planning and Soil Genesis zulkarnain_chairuddin@yahoo.com</t>
+          <t>Soil Mineralogy for Genesis and Landslide syam_lias@yahoo.com</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1045,18 +1041,18 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Surni, S.Si, M.Si​</t>
+          <t>Dr. Ir. Zulkarnain, Chairuddin, MP​</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Environmental Management and Biodiversity surni.saja01@gmail.com</t>
+          <t>Landuse Planning and Soil Genesis zulkarnain_chairuddin@yahoo.com</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1078,18 +1074,18 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Randi Kurniawan, SE., M.Sc​</t>
+          <t>Dr. Surni, S.Si, M.Si​</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Spatial Econometrics and Development Economics randikurniawan@unhas.ac.id</t>
+          <t>Environmental Management and Biodiversity surni.saja01@gmail.com</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1111,18 +1107,18 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Salman Samir, SE, M.Sc​</t>
+          <t>Randi Kurniawan, SE., M.Sc​</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Blue Economy, Environmental Economy salmansamir@unhas.ac.id</t>
+          <t>Spatial Econometrics and Development Economics randikurniawan@unhas.ac.id</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1144,18 +1140,18 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Haniek Khoirunnissa, B.,SE., M.Sc., Ak​</t>
+          <t>Salman Samir, SE, M.Sc​</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Spatial finance, environmental finance haniek.baja@unhas.ac.id</t>
+          <t>Blue Economy, Environmental Economy salmansamir@unhas.ac.id</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1177,18 +1173,18 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Rizky Utami, SE., M.Acc.Fin., Ak​</t>
+          <t>Haniek Khoirunnissa, B.,SE., M.Sc., Ak​</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>climate finance, Environmental Social and Governance (ESG) Finance rizkyutami@unhas.ac.id</t>
+          <t>Spatial finance, environmental finance haniek.baja@unhas.ac.id</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1210,18 +1206,18 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Hermansyah, S.Kel., M.Si.,M.Sc</t>
+          <t>Rizky Utami, SE., M.Acc.Fin., Ak​</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Remote Sensing prasyad@gmail.com</t>
+          <t>climate finance, Environmental Social and Governance (ESG) Finance rizkyutami@unhas.ac.id</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1243,18 +1239,18 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Jamilah Abbas</t>
+          <t>Hermansyah, S.Kel., M.Si.,M.Sc</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Doctoral Student in Development Studies abbasj22p@student.unhas.ac.id</t>
+          <t>Remote Sensing prasyad@gmail.com</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1276,7 +1272,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Katti Syamsuddin</t>
+          <t>Jamilah Abbas</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1287,7 +1283,7 @@
       <c r="D16" s="12" t="n"/>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Doctoral Student in Agricultural Science</t>
+          <t>Doctoral Student in Development Studies abbasj22p@student.unhas.ac.id</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1309,7 +1305,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Sitti Kubangun</t>
+          <t>Katti Syamsuddin</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1342,7 +1338,7 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Rini Anggraini</t>
+          <t>Sitti Kubangun</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -1353,7 +1349,7 @@
       <c r="D18" s="12" t="n"/>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Master Student in Spatial Planning</t>
+          <t>Doctoral Student in Agricultural Science</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -1373,10 +1369,22 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Rini Anggraini</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D19" s="12" t="n"/>
-      <c r="E19" s="11" t="n"/>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Master Student in Spatial Planning</t>
+        </is>
+      </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
@@ -1384,7 +1392,11 @@
       <c r="J19" s="12" t="n"/>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="12" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1573,15 +1585,32 @@
       <c r="L30" s="12" t="n"/>
       <c r="M30" s="12" t="n"/>
     </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
